--- a/hourly datasets/PlantID_year-5final.xlsx
+++ b/hourly datasets/PlantID_year-5final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,10 +791,10 @@
         <v>4042</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7824186798939284</v>
+        <v>0.1899359034657655</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7477084052281951</v>
+        <v>0.1976845004112108</v>
       </c>
     </row>
     <row r="34">
@@ -909,1200 +909,1233 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3406</v>
+        <v>3648</v>
       </c>
       <c r="B44" t="n">
-        <v>0.6081653225996022</v>
+        <v>0.3926888422002566</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3188676570365236</v>
+        <v>0.1894989806298726</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3797161927839146</v>
+        <v>0.6081653225996022</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3625697567401865</v>
+        <v>0.3188676570365236</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3399</v>
+        <v>3403</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3350997414693782</v>
+        <v>0.3797161927839146</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1430390550709021</v>
+        <v>0.3625697567401865</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3393</v>
+        <v>3399</v>
       </c>
       <c r="B47" t="n">
-        <v>0.3994901933580033</v>
+        <v>0.3350997414693782</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3644340262140048</v>
+        <v>0.1430390550709021</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3181</v>
+        <v>3393</v>
       </c>
       <c r="B48" t="n">
-        <v>0.3217889857220987</v>
+        <v>0.3994901933580033</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2284647458705261</v>
+        <v>0.3644340262140048</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3179</v>
+        <v>3181</v>
       </c>
       <c r="B49" t="n">
-        <v>0.3569838548117843</v>
+        <v>0.3217889857220987</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3620352602138258</v>
+        <v>0.2284647458705261</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3178</v>
+        <v>3179</v>
       </c>
       <c r="B50" t="n">
-        <v>0.3275663572897488</v>
+        <v>0.3569838548117843</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1898383704322337</v>
+        <v>0.3620352602138258</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3140</v>
+        <v>3178</v>
       </c>
       <c r="B51" t="n">
-        <v>0.337666493389861</v>
+        <v>0.3275663572897488</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3027113429131532</v>
+        <v>0.1898383704322337</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3131</v>
+        <v>3152</v>
       </c>
       <c r="B52" t="n">
-        <v>0.351105392634392</v>
+        <v>0.5546548798303321</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3591634049800527</v>
+        <v>0.3912442488943041</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3118</v>
+        <v>3148</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3473234575840232</v>
+        <v>0.2965615218757875</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3052546328180005</v>
+        <v>0.3013116440409568</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3113</v>
+        <v>3140</v>
       </c>
       <c r="B54" t="n">
-        <v>0.3529096989096496</v>
+        <v>0.337666493389861</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1632352768952993</v>
+        <v>0.3027113429131532</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2878</v>
+        <v>3131</v>
       </c>
       <c r="B55" t="n">
-        <v>0.369479057198514</v>
+        <v>0.351105392634392</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3708281215482347</v>
+        <v>0.3591634049800527</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2876</v>
+        <v>3118</v>
       </c>
       <c r="B56" t="n">
-        <v>0.3776694247978779</v>
+        <v>0.3473234575840232</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3603154521916198</v>
+        <v>0.3052546328180005</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2872</v>
+        <v>3113</v>
       </c>
       <c r="B57" t="n">
-        <v>0.3625406720542218</v>
+        <v>0.3529096989096496</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3260106814848599</v>
+        <v>0.1632352768952993</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2866</v>
+        <v>2878</v>
       </c>
       <c r="B58" t="n">
-        <v>0.3526714357011489</v>
+        <v>0.369479057198514</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2595376673622529</v>
+        <v>0.3708281215482347</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2861</v>
+        <v>2876</v>
       </c>
       <c r="B59" t="n">
-        <v>0.3477934470921597</v>
+        <v>0.3776694247978779</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2133136767445464</v>
+        <v>0.3603154521916198</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2857</v>
+        <v>2872</v>
       </c>
       <c r="B60" t="n">
-        <v>0.281129569897734</v>
+        <v>0.3624840521508431</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2186496650980376</v>
+        <v>0.3259996695515429</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2850</v>
+        <v>2866</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3433329220854273</v>
+        <v>0.3526714357011489</v>
       </c>
       <c r="C61" t="n">
-        <v>0.343753979504991</v>
+        <v>0.2595376673622529</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2843</v>
+        <v>2861</v>
       </c>
       <c r="B62" t="n">
-        <v>0.3252442778848884</v>
+        <v>0.3477934470921597</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2083697635410966</v>
+        <v>0.2133136767445464</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2840</v>
+        <v>2857</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3794182838440334</v>
+        <v>0.281129569897734</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3575590356340594</v>
+        <v>0.2186496650980376</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2837</v>
+        <v>2850</v>
       </c>
       <c r="B64" t="n">
-        <v>0.3884417201040438</v>
+        <v>0.3433329220854273</v>
       </c>
       <c r="C64" t="n">
-        <v>0.3110347034902847</v>
+        <v>0.343753979504991</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2836</v>
+        <v>2843</v>
       </c>
       <c r="B65" t="n">
-        <v>0.3369433616750324</v>
+        <v>0.3252442778848884</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1515793600707123</v>
+        <v>0.2083697635410966</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2835</v>
+        <v>2840</v>
       </c>
       <c r="B66" t="n">
-        <v>0.4299181261618698</v>
+        <v>0.3794182838440334</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3541535004374682</v>
+        <v>0.3575590356340594</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2832</v>
+        <v>2837</v>
       </c>
       <c r="B67" t="n">
-        <v>0.3510102084867193</v>
+        <v>0.3884417201040438</v>
       </c>
       <c r="C67" t="n">
-        <v>0.2863593208864377</v>
+        <v>0.3110347034902847</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2830</v>
+        <v>2836</v>
       </c>
       <c r="B68" t="n">
-        <v>0.3535494087983278</v>
+        <v>0.3369340771662647</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3324147205739544</v>
+        <v>0.1516074606744782</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2828</v>
+        <v>2835</v>
       </c>
       <c r="B69" t="n">
-        <v>0.3588371502263346</v>
+        <v>0.4299181261618698</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2864663327899014</v>
+        <v>0.3541535004374682</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2594</v>
+        <v>2832</v>
       </c>
       <c r="B70" t="n">
-        <v>0.9232630873494789</v>
+        <v>0.3510102084867193</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2556332247648307</v>
+        <v>0.2863593208864377</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2554</v>
+        <v>2830</v>
       </c>
       <c r="B71" t="n">
-        <v>0.3821884800577424</v>
+        <v>0.3535494087983278</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1867713941993695</v>
+        <v>0.3324147205739544</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2549</v>
+        <v>2828</v>
       </c>
       <c r="B72" t="n">
-        <v>0.2949961061059678</v>
+        <v>0.3588371502263346</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2781918649299595</v>
+        <v>0.2864663327899014</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2527</v>
+        <v>2594</v>
       </c>
       <c r="B73" t="n">
-        <v>0.4098863214406124</v>
+        <v>0.9223480455473743</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1227435804219945</v>
+        <v>0.2556506736491575</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2517</v>
+        <v>2554</v>
       </c>
       <c r="B74" t="n">
-        <v>0.3663004271672184</v>
+        <v>0.3821884800577424</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2933406696082255</v>
+        <v>0.1867713941993695</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2516</v>
+        <v>2549</v>
       </c>
       <c r="B75" t="n">
-        <v>0.3456634065261896</v>
+        <v>0.2949961061059678</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3012155931624207</v>
+        <v>0.2781918649299595</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2378</v>
+        <v>2535</v>
       </c>
       <c r="B76" t="n">
-        <v>0.3453780315850363</v>
+        <v>0.3646804787964404</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3038938519228676</v>
+        <v>0.3264977314482854</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2364</v>
+        <v>2527</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3525431216392524</v>
+        <v>0.4098863214406124</v>
       </c>
       <c r="C77" t="n">
-        <v>0.2894672639014496</v>
+        <v>0.1227435804219945</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2168</v>
+        <v>2517</v>
       </c>
       <c r="B78" t="n">
-        <v>0.328708041209899</v>
+        <v>0.3663004271672184</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3300134796977693</v>
+        <v>0.2933406696082255</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2167</v>
+        <v>2516</v>
       </c>
       <c r="B79" t="n">
-        <v>0.347242256606984</v>
+        <v>0.3456634065261896</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3366660226245398</v>
+        <v>0.3012155931624207</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2161</v>
+        <v>2378</v>
       </c>
       <c r="B80" t="n">
-        <v>0.3073561893190898</v>
+        <v>0.3453780315850363</v>
       </c>
       <c r="C80" t="n">
-        <v>0.306355634535508</v>
+        <v>0.3038938519228676</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2107</v>
+        <v>2364</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3564376917044341</v>
+        <v>0.3525431216392524</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2014334174200204</v>
+        <v>0.2894672639014496</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2104</v>
+        <v>2168</v>
       </c>
       <c r="B82" t="n">
-        <v>0.3895049259438744</v>
+        <v>0.328708041209899</v>
       </c>
       <c r="C82" t="n">
-        <v>0.2553359531861112</v>
+        <v>0.3300134796977693</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2103</v>
+        <v>2167</v>
       </c>
       <c r="B83" t="n">
-        <v>0.3289174670030052</v>
+        <v>0.347242256606984</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3240016156437775</v>
+        <v>0.3366660226245398</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2094</v>
+        <v>2161</v>
       </c>
       <c r="B84" t="n">
-        <v>0.3307078980575056</v>
+        <v>0.3073561893190898</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2470961413476412</v>
+        <v>0.306355634535508</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2080</v>
+        <v>2107</v>
       </c>
       <c r="B85" t="n">
-        <v>0.2898452909214255</v>
+        <v>0.3564376917044341</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2693312333619846</v>
+        <v>0.2014334174200204</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2079</v>
+        <v>2104</v>
       </c>
       <c r="B86" t="n">
-        <v>0.3372433879823832</v>
+        <v>0.3895049259438744</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3402666492379657</v>
+        <v>0.2553359531861112</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2076</v>
+        <v>2103</v>
       </c>
       <c r="B87" t="n">
-        <v>0.3958070843343512</v>
+        <v>0.3289174670030052</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1957216615609177</v>
+        <v>0.3240016156437775</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2049</v>
+        <v>2094</v>
       </c>
       <c r="B88" t="n">
-        <v>0.3664351696017946</v>
+        <v>0.3307078980575056</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3039698100824458</v>
+        <v>0.2470961413476412</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1912</v>
+        <v>2080</v>
       </c>
       <c r="B89" t="n">
-        <v>0.3021888497082498</v>
+        <v>0.2898452909214255</v>
       </c>
       <c r="C89" t="n">
-        <v>0.1909667217377758</v>
+        <v>0.2693312333619846</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1723</v>
+        <v>2079</v>
       </c>
       <c r="B90" t="n">
-        <v>0.3464204050467496</v>
+        <v>0.3372433879823832</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3432451065086399</v>
+        <v>0.3402666492379657</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1720</v>
+        <v>2076</v>
       </c>
       <c r="B91" t="n">
-        <v>0.3565804617434754</v>
+        <v>0.3958070843343512</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3402237162917815</v>
+        <v>0.1957216615609177</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1710</v>
+        <v>2049</v>
       </c>
       <c r="B92" t="n">
-        <v>0.3651656580694664</v>
+        <v>0.3664351696017946</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3225632265749276</v>
+        <v>0.3039698100824458</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1702</v>
+        <v>1912</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3764542830846391</v>
+        <v>0.3021888497082498</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3598111216254937</v>
+        <v>0.1909667217377758</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1626</v>
+        <v>1723</v>
       </c>
       <c r="B94" t="n">
-        <v>0.357139320137509</v>
+        <v>0.3464204050467496</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2637338918139669</v>
+        <v>0.3432451065086399</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1619</v>
+        <v>1720</v>
       </c>
       <c r="B95" t="n">
-        <v>0.4098737004753095</v>
+        <v>0.3565804617434754</v>
       </c>
       <c r="C95" t="n">
-        <v>0.376655891223158</v>
+        <v>0.3402237162917815</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1606</v>
+        <v>1710</v>
       </c>
       <c r="B96" t="n">
-        <v>0.4054309772442743</v>
+        <v>0.3651656580694664</v>
       </c>
       <c r="C96" t="n">
-        <v>0.272981955302236</v>
+        <v>0.3225632265749276</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1573</v>
+        <v>1702</v>
       </c>
       <c r="B97" t="n">
-        <v>0.4240297565285431</v>
+        <v>0.3764542830846391</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1256978206501678</v>
+        <v>0.3598111216254937</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1571</v>
+        <v>1626</v>
       </c>
       <c r="B98" t="n">
-        <v>0.3515771891659047</v>
+        <v>0.357139320137509</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3045382009714929</v>
+        <v>0.2637338918139669</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1570</v>
+        <v>1619</v>
       </c>
       <c r="B99" t="n">
-        <v>0.3216390089905403</v>
+        <v>0.4098737004753095</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2214471639605749</v>
+        <v>0.376655891223158</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1552</v>
+        <v>1606</v>
       </c>
       <c r="B100" t="n">
-        <v>0.3012247405795566</v>
+        <v>0.4054309772442743</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1578897158661545</v>
+        <v>0.272981955302236</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1384</v>
+        <v>1573</v>
       </c>
       <c r="B101" t="n">
-        <v>0.3669224493412275</v>
+        <v>0.4240297565285431</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2259765394290166</v>
+        <v>0.1256978206501678</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1382</v>
+        <v>1571</v>
       </c>
       <c r="B102" t="n">
-        <v>0.363290841620831</v>
+        <v>0.3515771891659047</v>
       </c>
       <c r="C102" t="n">
-        <v>0.04630106772167087</v>
+        <v>0.3045382009714929</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1381</v>
+        <v>1570</v>
       </c>
       <c r="B103" t="n">
-        <v>0.3668600877894126</v>
+        <v>0.3216390089905403</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3329853481097314</v>
+        <v>0.2214471639605749</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1379</v>
+        <v>1552</v>
       </c>
       <c r="B104" t="n">
-        <v>0.2793138114026114</v>
+        <v>0.3012247405795566</v>
       </c>
       <c r="C104" t="n">
-        <v>0.2146571483550322</v>
+        <v>0.1578897158661545</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B105" t="n">
-        <v>0.4844666851906509</v>
+        <v>0.3669224493412275</v>
       </c>
       <c r="C105" t="n">
-        <v>0.207604035415975</v>
+        <v>0.2259765394290166</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="B106" t="n">
-        <v>0.4411933389263253</v>
+        <v>0.363290841620831</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1379510280831988</v>
+        <v>0.04630106772167087</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1357</v>
+        <v>1381</v>
       </c>
       <c r="B107" t="n">
-        <v>0.2935729852909476</v>
+        <v>0.3668600877894126</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1618852517136486</v>
+        <v>0.3329853481097314</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1356</v>
+        <v>1379</v>
       </c>
       <c r="B108" t="n">
-        <v>0.3629680822156559</v>
+        <v>0.2793138114026114</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2268736178190179</v>
+        <v>0.2146571483550322</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1355</v>
+        <v>1378</v>
       </c>
       <c r="B109" t="n">
-        <v>0.3309346177964644</v>
+        <v>0.4844666851906509</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2974624905930475</v>
+        <v>0.207604035415975</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1295</v>
+        <v>1374</v>
       </c>
       <c r="B110" t="n">
-        <v>0.3681437367799818</v>
+        <v>0.4411933389263253</v>
       </c>
       <c r="C110" t="n">
-        <v>0.2434563623102982</v>
+        <v>0.1379510280831988</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1241</v>
+        <v>1357</v>
       </c>
       <c r="B111" t="n">
-        <v>0.3080239398204193</v>
+        <v>0.2935729852909476</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1473971913155392</v>
+        <v>0.1618852517136486</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1104</v>
+        <v>1356</v>
       </c>
       <c r="B112" t="n">
-        <v>0.3460869864855552</v>
+        <v>0.3629680822156559</v>
       </c>
       <c r="C112" t="n">
-        <v>0.1587823670799392</v>
+        <v>0.2268736178190179</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1081</v>
+        <v>1355</v>
       </c>
       <c r="B113" t="n">
-        <v>0.4210469883460745</v>
+        <v>0.3309346177964644</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2348647688883451</v>
+        <v>0.2974624905930475</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1073</v>
+        <v>1295</v>
       </c>
       <c r="B114" t="n">
-        <v>0.4177560581234087</v>
+        <v>0.3681437367799818</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1129073877607587</v>
+        <v>0.2434563623102982</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1048</v>
+        <v>1241</v>
       </c>
       <c r="B115" t="n">
-        <v>0.3589499003075336</v>
+        <v>0.3080239398204193</v>
       </c>
       <c r="C115" t="n">
-        <v>0.1559943768226723</v>
+        <v>0.1473971913155392</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1043</v>
+        <v>1104</v>
       </c>
       <c r="B116" t="n">
-        <v>0.3650582382097938</v>
+        <v>0.3460869864855552</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4958270306222222</v>
+        <v>0.1587823670799392</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1012</v>
+        <v>1081</v>
       </c>
       <c r="B117" t="n">
-        <v>0.3516568004615716</v>
+        <v>0.4210469883460745</v>
       </c>
       <c r="C117" t="n">
-        <v>0.3261285510119878</v>
+        <v>0.2348647688883451</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1010</v>
+        <v>1048</v>
       </c>
       <c r="B118" t="n">
-        <v>0.347803719174677</v>
+        <v>0.3589499003075336</v>
       </c>
       <c r="C118" t="n">
-        <v>0.3581886427798633</v>
+        <v>0.1559943768226723</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1008</v>
+        <v>1043</v>
       </c>
       <c r="B119" t="n">
-        <v>0.3750803463378901</v>
+        <v>0.3650582382097938</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2596657065481903</v>
+        <v>0.4958270306222222</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="B120" t="n">
-        <v>0.3540452759583777</v>
+        <v>0.3516568004615716</v>
       </c>
       <c r="C120" t="n">
-        <v>0.3251226295816934</v>
+        <v>0.3261285510119878</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="B121" t="n">
-        <v>0.358086273066074</v>
+        <v>0.347803719174677</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2689572808377956</v>
+        <v>0.3581886427798633</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>994</v>
+        <v>1008</v>
       </c>
       <c r="B122" t="n">
-        <v>0.3302489814071</v>
+        <v>0.3750803463378901</v>
       </c>
       <c r="C122" t="n">
-        <v>0.3195644891973971</v>
+        <v>0.2596657065481903</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="B123" t="n">
-        <v>0.3811352610768651</v>
+        <v>0.3540452759583777</v>
       </c>
       <c r="C123" t="n">
-        <v>0.3519099099883118</v>
+        <v>0.3251226295816934</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>990</v>
+        <v>995</v>
       </c>
       <c r="B124" t="n">
-        <v>0.3580232901520428</v>
+        <v>0.358086273066074</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2681259085979236</v>
+        <v>0.2689572808377956</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="B125" t="n">
-        <v>0.3841926705887183</v>
+        <v>0.3302489814071</v>
       </c>
       <c r="C125" t="n">
-        <v>0.2603959862879861</v>
+        <v>0.3195644891973971</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="B126" t="n">
-        <v>0.3876880134291685</v>
+        <v>0.3811352610768651</v>
       </c>
       <c r="C126" t="n">
-        <v>0.3540329521434992</v>
+        <v>0.3519099099883118</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>898</v>
+        <v>990</v>
       </c>
       <c r="B127" t="n">
-        <v>0.5115107709985736</v>
+        <v>0.3580232901520428</v>
       </c>
       <c r="C127" t="n">
-        <v>0.2967417310874794</v>
+        <v>0.2681259085979236</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>897</v>
+        <v>988</v>
       </c>
       <c r="B128" t="n">
-        <v>0.3118600173462527</v>
+        <v>0.3841926705887183</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2070189662725886</v>
+        <v>0.2603959862879861</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>892</v>
+        <v>983</v>
       </c>
       <c r="B129" t="n">
-        <v>0.3504047902460523</v>
+        <v>0.3876880134291685</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2064178789912281</v>
+        <v>0.3540329521434992</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="B130" t="n">
-        <v>0.3572117881186065</v>
+        <v>0.5115107709985736</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2563712130177653</v>
+        <v>0.2967417310874794</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="B131" t="n">
-        <v>0.3308272498810406</v>
+        <v>0.3118600173462527</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3193416329530831</v>
+        <v>0.2070189662725886</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>876</v>
+        <v>892</v>
       </c>
       <c r="B132" t="n">
-        <v>0.4126113671719062</v>
+        <v>0.3504047902460523</v>
       </c>
       <c r="C132" t="n">
-        <v>0.2086686432005373</v>
+        <v>0.2064178789912281</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="B133" t="n">
-        <v>0.3473510735948819</v>
+        <v>0.3572117881186065</v>
       </c>
       <c r="C133" t="n">
-        <v>0.3094689044471209</v>
+        <v>0.2563712130177653</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>864</v>
+        <v>887</v>
       </c>
       <c r="B134" t="n">
-        <v>0.323541307249837</v>
+        <v>0.3308272498810406</v>
       </c>
       <c r="C134" t="n">
-        <v>0.2379894155895212</v>
+        <v>0.3193416329530831</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="B135" t="n">
-        <v>0.3106702622882725</v>
+        <v>0.4126113671719062</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1920878776622009</v>
+        <v>0.2086686432005373</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="B136" t="n">
-        <v>0.4950783493118512</v>
+        <v>0.3473510735948819</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1991732923717136</v>
+        <v>0.3094689044471209</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B137" t="n">
-        <v>0.3064547503279703</v>
+        <v>0.323541307249837</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1749750542175869</v>
+        <v>0.2379894155895212</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>733</v>
+        <v>863</v>
       </c>
       <c r="B138" t="n">
-        <v>0.4002092710655875</v>
+        <v>0.3106702622882725</v>
       </c>
       <c r="C138" t="n">
-        <v>0.3562491197859778</v>
+        <v>0.1920878776622009</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>728</v>
+        <v>862</v>
       </c>
       <c r="B139" t="n">
-        <v>0.3375460938298391</v>
+        <v>0.4950783493118512</v>
       </c>
       <c r="C139" t="n">
-        <v>0.294425477771501</v>
+        <v>0.1991732923717136</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>727</v>
+        <v>861</v>
       </c>
       <c r="B140" t="n">
-        <v>0.505531634959922</v>
+        <v>0.3064547503279703</v>
       </c>
       <c r="C140" t="n">
-        <v>0.193100805461479</v>
+        <v>0.1749750542175869</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>710</v>
+        <v>733</v>
       </c>
       <c r="B141" t="n">
-        <v>0.379943953322869</v>
+        <v>0.4002092710655875</v>
       </c>
       <c r="C141" t="n">
-        <v>0.08404288861300774</v>
+        <v>0.3562491197859778</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>709</v>
+        <v>728</v>
       </c>
       <c r="B142" t="n">
-        <v>0.3645779121458736</v>
+        <v>0.3375460938298391</v>
       </c>
       <c r="C142" t="n">
-        <v>0.3184158114393266</v>
+        <v>0.294425477771501</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>708</v>
+        <v>727</v>
       </c>
       <c r="B143" t="n">
-        <v>0.3339413851777939</v>
+        <v>0.505531634959922</v>
       </c>
       <c r="C143" t="n">
-        <v>0.2798314914285459</v>
+        <v>0.193100805461479</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B144" t="n">
-        <v>0.365094891301132</v>
+        <v>0.379943953322869</v>
       </c>
       <c r="C144" t="n">
-        <v>0.3611024877373562</v>
+        <v>0.08404288861300774</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="B145" t="n">
-        <v>0.3131411203079891</v>
+        <v>0.3645779121458736</v>
       </c>
       <c r="C145" t="n">
-        <v>0.2577908174097741</v>
+        <v>0.3184158114393266</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>645</v>
+        <v>708</v>
       </c>
       <c r="B146" t="n">
-        <v>0.3459289812680889</v>
+        <v>0.3339413851777939</v>
       </c>
       <c r="C146" t="n">
-        <v>0.3089397303231735</v>
+        <v>0.2798314914285459</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>642</v>
+        <v>703</v>
       </c>
       <c r="B147" t="n">
-        <v>0.2564508522775998</v>
+        <v>0.365094891301132</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1533984858791717</v>
+        <v>0.3611024877373562</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>641</v>
+        <v>699</v>
       </c>
       <c r="B148" t="n">
-        <v>0.3085486849068858</v>
+        <v>0.3131411203079891</v>
       </c>
       <c r="C148" t="n">
-        <v>0.2522717550407838</v>
+        <v>0.2577908174097741</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>56</v>
+        <v>645</v>
       </c>
       <c r="B149" t="n">
-        <v>0.3229707602317733</v>
+        <v>0.3456101174754895</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1207425987360456</v>
+        <v>0.3088622009420965</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>47</v>
+        <v>642</v>
       </c>
       <c r="B150" t="n">
-        <v>0.3594231411001607</v>
+        <v>0.2564508522775998</v>
       </c>
       <c r="C150" t="n">
-        <v>0.366488365190525</v>
+        <v>0.1533984858791717</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>26</v>
+        <v>641</v>
       </c>
       <c r="B151" t="n">
-        <v>0.3457479358123071</v>
+        <v>0.3085486849068858</v>
       </c>
       <c r="C151" t="n">
-        <v>0.3105899521638096</v>
+        <v>0.2522717550407838</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
+        <v>56</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.3229707602317733</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.1207425987360456</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>47</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.3594231411001607</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.366488365190525</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>26</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.3457479358123071</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.3105899521638096</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
         <v>7</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B155" t="n">
         <v>0.399642350832865</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C155" t="n">
         <v>0.2255467831244189</v>
       </c>
     </row>

--- a/hourly datasets/PlantID_year-5final.xlsx
+++ b/hourly datasets/PlantID_year-5final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>CoefCat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>intercept</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cat_value_current</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>efficiencyMax</t>
         </is>
       </c>
     </row>
@@ -450,10 +465,21 @@
         <v>8226</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3552923712726608</v>
-      </c>
-      <c r="C2" t="n">
+        <v>0.3554432463984214</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>105%&gt;gen/cap&gt;100%</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>0.1551712454460489</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2862983427215751</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3837062598639296</v>
       </c>
     </row>
     <row r="3">
@@ -463,8 +489,19 @@
       <c r="B3" t="n">
         <v>0.3474114337440978</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>0.1394513239211282</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3474114337440978</v>
       </c>
     </row>
     <row r="4">
@@ -474,8 +511,19 @@
       <c r="B4" t="n">
         <v>0.2782277944379779</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>0.2603651123082333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2671407720052213</v>
       </c>
     </row>
     <row r="5">
@@ -485,8 +533,19 @@
       <c r="B5" t="n">
         <v>0.4055961751619946</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>85%&gt;gen/cap&gt;80%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>0.2698803352849158</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3287809805955695</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3913765507535085</v>
       </c>
     </row>
     <row r="6">
@@ -496,8 +555,19 @@
       <c r="B6" t="n">
         <v>0.2785043514278274</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>0.1302831355515159</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2785043514278274</v>
       </c>
     </row>
     <row r="7">
@@ -507,8 +577,19 @@
       <c r="B7" t="n">
         <v>0.3090181855324101</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>70%&gt;gen/cap&gt;65%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>0.1714851378538474</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3242557738547276</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2993237678647658</v>
       </c>
     </row>
     <row r="8">
@@ -518,8 +599,19 @@
       <c r="B8" t="n">
         <v>0.3401975482949796</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>75%&gt;gen/cap&gt;70%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>0.335890379181976</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3263565755623398</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3284023289197232</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +619,21 @@
         <v>6257</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3343225803395934</v>
-      </c>
-      <c r="C9" t="n">
+        <v>0.328846638312652</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>0.3432294565610152</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3587454625663571</v>
       </c>
     </row>
     <row r="10">
@@ -540,8 +643,19 @@
       <c r="B10" t="n">
         <v>0.3658709279740636</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>0.2412445521540299</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3655469927093403</v>
       </c>
     </row>
     <row r="11">
@@ -551,8 +665,19 @@
       <c r="B11" t="n">
         <v>0.3155112536720381</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>0.2448229558085094</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3059813346586426</v>
       </c>
     </row>
     <row r="12">
@@ -562,8 +687,19 @@
       <c r="B12" t="n">
         <v>0.3879401210410856</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20%&gt;gen/cap&gt;15%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>0.3552805623932609</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2963646942557381</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4061367829724308</v>
       </c>
     </row>
     <row r="13">
@@ -573,8 +709,19 @@
       <c r="B13" t="n">
         <v>0.4104060715221152</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>75%&gt;gen/cap&gt;70%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>0.4059912716054223</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3263565755623398</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3986108521468588</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +729,21 @@
         <v>6101</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2838538938680598</v>
-      </c>
-      <c r="C14" t="n">
+        <v>0.2864410624847601</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>105%&gt;gen/cap&gt;100%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>0.0667309816958766</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2862983427215751</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3147040759502683</v>
       </c>
     </row>
     <row r="15">
@@ -595,8 +753,19 @@
       <c r="B15" t="n">
         <v>0.4125691066352672</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25%&gt;gen/cap&gt;20%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>0.4038165477166723</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3086240115132508</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4185064513090998</v>
       </c>
     </row>
     <row r="16">
@@ -606,8 +775,19 @@
       <c r="B16" t="n">
         <v>0.3474616674149523</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20%&gt;gen/cap&gt;15%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>0.3248053007491101</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2963646942557381</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3656583293462976</v>
       </c>
     </row>
     <row r="17">
@@ -617,8 +797,19 @@
       <c r="B17" t="n">
         <v>0.3244554527198928</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>0.2542256669473548</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3244554527198927</v>
       </c>
     </row>
     <row r="18">
@@ -628,8 +819,19 @@
       <c r="B18" t="n">
         <v>0.3116993936044473</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>90%&gt;gen/cap&gt;85%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>0.3029886701291787</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3283053907823258</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2979553590092048</v>
       </c>
     </row>
     <row r="19">
@@ -639,8 +841,19 @@
       <c r="B19" t="n">
         <v>0.4055368704473684</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>0.08907431371578098</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.396006951433973</v>
       </c>
     </row>
     <row r="20">
@@ -650,8 +863,19 @@
       <c r="B20" t="n">
         <v>0.3793361856980768</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>0.2968168894270694</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3666267087052021</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +883,21 @@
         <v>6041</v>
       </c>
       <c r="B21" t="n">
-        <v>0.4201693435208001</v>
-      </c>
-      <c r="C21" t="n">
+        <v>0.3520321833152392</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>0.2518873463203275</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3517082480505159</v>
       </c>
     </row>
     <row r="22">
@@ -672,8 +907,19 @@
       <c r="B22" t="n">
         <v>0.424500240611838</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>35%&gt;gen/cap&gt;30%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>0.2359966964532038</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.318230412532292</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4208311842666294</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +927,21 @@
         <v>6018</v>
       </c>
       <c r="B23" t="n">
-        <v>0.3426884131466626</v>
-      </c>
-      <c r="C23" t="n">
+        <v>0.3453793050565521</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>105%&gt;gen/cap&gt;100%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>0.3439988212068588</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2862983427215751</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.3736423185220603</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +949,21 @@
         <v>6017</v>
       </c>
       <c r="B24" t="n">
-        <v>0.239726672398591</v>
-      </c>
-      <c r="C24" t="n">
+        <v>0.1922194179547909</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>50%&gt;gen/cap&gt;45%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>0.05850200691513129</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.32492994165991</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1818508324819643</v>
       </c>
     </row>
     <row r="25">
@@ -705,8 +973,19 @@
       <c r="B25" t="n">
         <v>0.3279986293495945</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>0.2087637470975833</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.318468710336199</v>
       </c>
     </row>
     <row r="26">
@@ -716,8 +995,19 @@
       <c r="B26" t="n">
         <v>0.3125579423528549</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>80%&gt;gen/cap&gt;75%</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>0.1582578159593929</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3273807104656135</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.2997385880743249</v>
       </c>
     </row>
     <row r="27">
@@ -727,8 +1017,19 @@
       <c r="B27" t="n">
         <v>0.3876658048544019</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0.2653533481805699</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.3781358858410064</v>
       </c>
     </row>
     <row r="28">
@@ -738,8 +1039,19 @@
       <c r="B28" t="n">
         <v>0.3189621403650598</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>50%&gt;gen/cap&gt;45%</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>0.2966724787837601</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.32492994165991</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.3085935548922332</v>
       </c>
     </row>
     <row r="29">
@@ -749,8 +1061,19 @@
       <c r="B29" t="n">
         <v>0.3149123188432593</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>0.2552556915990486</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3022028418503847</v>
       </c>
     </row>
     <row r="30">
@@ -758,10 +1081,21 @@
         <v>4057</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3272916066229293</v>
-      </c>
-      <c r="C30" t="n">
+        <v>0.2939189585213312</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>60%&gt;gen/cap&gt;55%</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>0.2430876902308514</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.3252091815446558</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2832711331637587</v>
       </c>
     </row>
     <row r="31">
@@ -771,8 +1105,19 @@
       <c r="B31" t="n">
         <v>0.3634608149789025</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>0.2427693364641491</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.3562797358676608</v>
       </c>
     </row>
     <row r="32">
@@ -782,8 +1127,19 @@
       <c r="B32" t="n">
         <v>0.3410360637700542</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>0.2388637394723109</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.3338549846588125</v>
       </c>
     </row>
     <row r="33">
@@ -793,8 +1149,19 @@
       <c r="B33" t="n">
         <v>0.1899359034657655</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>70%&gt;gen/cap&gt;65%</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>0.1976845004112108</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3242557738547276</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1802414857981213</v>
       </c>
     </row>
     <row r="34">
@@ -804,8 +1171,19 @@
       <c r="B34" t="n">
         <v>0.3837145768750915</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>0.3681930664959028</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3837145768750915</v>
       </c>
     </row>
     <row r="35">
@@ -815,8 +1193,19 @@
       <c r="B35" t="n">
         <v>0.2913092643546397</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>60%&gt;gen/cap&gt;55%</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>0.2292177869753731</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3252091815446558</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2806614389970672</v>
       </c>
     </row>
     <row r="36">
@@ -826,8 +1215,19 @@
       <c r="B36" t="n">
         <v>0.3635269092423447</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>70%&gt;gen/cap&gt;65%</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>0.2865477947335922</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.3242557738547276</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.3538324915747004</v>
       </c>
     </row>
     <row r="37">
@@ -837,8 +1237,19 @@
       <c r="B37" t="n">
         <v>0.3775941450686754</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>35%&gt;gen/cap&gt;30%</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>0.2869028321792945</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.318230412532292</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.3739250887234667</v>
       </c>
     </row>
     <row r="38">
@@ -848,8 +1259,19 @@
       <c r="B38" t="n">
         <v>0.3940836482872148</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20%&gt;gen/cap&gt;15%</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>0.3939717587621016</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2963646942557381</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.41228031021856</v>
       </c>
     </row>
     <row r="39">
@@ -859,8 +1281,19 @@
       <c r="B39" t="n">
         <v>0.3366353580817228</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>60%&gt;gen/cap&gt;55%</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>0.1801983232476043</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.3252091815446558</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.3259875327241504</v>
       </c>
     </row>
     <row r="40">
@@ -870,8 +1303,19 @@
       <c r="B40" t="n">
         <v>0.2849652984772375</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>0.1400923994477108</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2777842193659957</v>
       </c>
     </row>
     <row r="41">
@@ -881,8 +1325,19 @@
       <c r="B41" t="n">
         <v>0.3405143372823186</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>0.3091382114898137</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.3401904020175953</v>
       </c>
     </row>
     <row r="42">
@@ -892,8 +1347,19 @@
       <c r="B42" t="n">
         <v>0.3582672731998908</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>0.2424091346783407</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.3582672731998907</v>
       </c>
     </row>
     <row r="43">
@@ -903,8 +1369,19 @@
       <c r="B43" t="n">
         <v>0.3018999497704454</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>55%&gt;gen/cap&gt;50%</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>0.2108279717515211</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.3263837145832078</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.290077591374321</v>
       </c>
     </row>
     <row r="44">
@@ -912,10 +1389,21 @@
         <v>3648</v>
       </c>
       <c r="B44" t="n">
-        <v>0.3926888422002566</v>
-      </c>
-      <c r="C44" t="n">
+        <v>0.3364036783065826</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>0.1894989806298726</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3268737592931871</v>
       </c>
     </row>
     <row r="45">
@@ -925,8 +1413,19 @@
       <c r="B45" t="n">
         <v>0.6081653225996022</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>80%&gt;gen/cap&gt;75%</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>0.3188676570365236</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.3273807104656135</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5953459683210721</v>
       </c>
     </row>
     <row r="46">
@@ -936,8 +1435,19 @@
       <c r="B46" t="n">
         <v>0.3797161927839146</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>35%&gt;gen/cap&gt;30%</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>0.3625697567401865</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.318230412532292</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.376047136438706</v>
       </c>
     </row>
     <row r="47">
@@ -947,8 +1457,19 @@
       <c r="B47" t="n">
         <v>0.3350997414693782</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>0.1430390550709021</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.3279186623581364</v>
       </c>
     </row>
     <row r="48">
@@ -958,8 +1479,19 @@
       <c r="B48" t="n">
         <v>0.3994901933580033</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>50%&gt;gen/cap&gt;45%</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>0.3644340262140048</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.32492994165991</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.3891216078851767</v>
       </c>
     </row>
     <row r="49">
@@ -969,8 +1501,19 @@
       <c r="B49" t="n">
         <v>0.3217889857220987</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>70%&gt;gen/cap&gt;65%</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>0.2284647458705261</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.3242557738547276</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.3120945680544545</v>
       </c>
     </row>
     <row r="50">
@@ -980,8 +1523,19 @@
       <c r="B50" t="n">
         <v>0.3569838548117843</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>0.3620352602138258</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.3442743778189096</v>
       </c>
     </row>
     <row r="51">
@@ -989,10 +1543,21 @@
         <v>3178</v>
       </c>
       <c r="B51" t="n">
-        <v>0.3275663572897488</v>
-      </c>
-      <c r="C51" t="n">
+        <v>0.3382027626672374</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>115%&gt;gen/cap&gt;110%</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>0.1898383704322337</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.293848008898297</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.3589161099560237</v>
       </c>
     </row>
     <row r="52">
@@ -1002,8 +1567,19 @@
       <c r="B52" t="n">
         <v>0.5546548798303321</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>0.3912442488943041</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.5451249608169366</v>
       </c>
     </row>
     <row r="53">
@@ -1013,8 +1589,19 @@
       <c r="B53" t="n">
         <v>0.2965615218757875</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>50%&gt;gen/cap&gt;45%</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>0.3013116440409568</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.32492994165991</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.286192936402961</v>
       </c>
     </row>
     <row r="54">
@@ -1024,8 +1611,19 @@
       <c r="B54" t="n">
         <v>0.337666493389861</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>0.3027113429131532</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.337666493389861</v>
       </c>
     </row>
     <row r="55">
@@ -1033,10 +1631,21 @@
         <v>3131</v>
       </c>
       <c r="B55" t="n">
-        <v>0.351105392634392</v>
-      </c>
-      <c r="C55" t="n">
+        <v>0.3660697588336866</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>105%&gt;gen/cap&gt;100%</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>0.3591634049800527</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.2862983427215751</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.3943327722991949</v>
       </c>
     </row>
     <row r="56">
@@ -1046,8 +1655,19 @@
       <c r="B56" t="n">
         <v>0.3473234575840232</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>0.3052546328180005</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.3473234575840232</v>
       </c>
     </row>
     <row r="57">
@@ -1057,8 +1677,19 @@
       <c r="B57" t="n">
         <v>0.3529096989096496</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>85%&gt;gen/cap&gt;80%</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>0.1632352768952993</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.3287809805955695</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.3386900745011633</v>
       </c>
     </row>
     <row r="58">
@@ -1066,10 +1697,21 @@
         <v>2878</v>
       </c>
       <c r="B58" t="n">
-        <v>0.369479057198514</v>
-      </c>
-      <c r="C58" t="n">
+        <v>0.3776956187600237</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>105%&gt;gen/cap&gt;100%</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>0.3708281215482347</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.2862983427215751</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.4059586322255319</v>
       </c>
     </row>
     <row r="59">
@@ -1077,10 +1719,21 @@
         <v>2876</v>
       </c>
       <c r="B59" t="n">
-        <v>0.3776694247978779</v>
-      </c>
-      <c r="C59" t="n">
+        <v>0.4065165009848799</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>115%&gt;gen/cap&gt;110%</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>0.3603154521916198</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.293848008898297</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.4272298482736662</v>
       </c>
     </row>
     <row r="60">
@@ -1090,8 +1743,19 @@
       <c r="B60" t="n">
         <v>0.3624840521508431</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>85%&gt;gen/cap&gt;80%</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
         <v>0.3259996695515429</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.3287809805955695</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.3482644277423569</v>
       </c>
     </row>
     <row r="61">
@@ -1099,10 +1763,21 @@
         <v>2866</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3526714357011489</v>
-      </c>
-      <c r="C61" t="n">
+        <v>0.3381954202449502</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
         <v>0.2595376673622529</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.3271083978121936</v>
       </c>
     </row>
     <row r="62">
@@ -1112,8 +1787,19 @@
       <c r="B62" t="n">
         <v>0.3477934470921597</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>0.2133136767445464</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.3406123679809179</v>
       </c>
     </row>
     <row r="63">
@@ -1123,8 +1809,19 @@
       <c r="B63" t="n">
         <v>0.281129569897734</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>0.2186496650980376</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.2808056346330107</v>
       </c>
     </row>
     <row r="64">
@@ -1134,8 +1831,19 @@
       <c r="B64" t="n">
         <v>0.3433329220854273</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>0.343753979504991</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.3306234450925525</v>
       </c>
     </row>
     <row r="65">
@@ -1143,10 +1851,21 @@
         <v>2843</v>
       </c>
       <c r="B65" t="n">
-        <v>0.3252442778848884</v>
-      </c>
-      <c r="C65" t="n">
+        <v>0.3216735814571732</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>0.2083697635410966</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.3121436624437777</v>
       </c>
     </row>
     <row r="66">
@@ -1156,8 +1875,19 @@
       <c r="B66" t="n">
         <v>0.3794182838440334</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>25%&gt;gen/cap&gt;20%</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
         <v>0.3575590356340594</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.3086240115132508</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.3853556285178659</v>
       </c>
     </row>
     <row r="67">
@@ -1167,8 +1897,19 @@
       <c r="B67" t="n">
         <v>0.3884417201040438</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>0.3110347034902847</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.3884417201040438</v>
       </c>
     </row>
     <row r="68">
@@ -1178,8 +1919,19 @@
       <c r="B68" t="n">
         <v>0.3369340771662647</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
         <v>0.1516074606744782</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.3274041581528692</v>
       </c>
     </row>
     <row r="69">
@@ -1187,10 +1939,21 @@
         <v>2835</v>
       </c>
       <c r="B69" t="n">
-        <v>0.4299181261618698</v>
-      </c>
-      <c r="C69" t="n">
+        <v>0.3894181017602683</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>0.3541535004374682</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.3822370226490266</v>
       </c>
     </row>
     <row r="70">
@@ -1200,8 +1963,19 @@
       <c r="B70" t="n">
         <v>0.3510102084867193</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
         <v>0.2863593208864377</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.3438291293754775</v>
       </c>
     </row>
     <row r="71">
@@ -1209,10 +1983,21 @@
         <v>2830</v>
       </c>
       <c r="B71" t="n">
-        <v>0.3535494087983278</v>
-      </c>
-      <c r="C71" t="n">
+        <v>0.3436931260412936</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>50%&gt;gen/cap&gt;45%</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>0.3324147205739544</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.32492994165991</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.3333245405684669</v>
       </c>
     </row>
     <row r="72">
@@ -1222,8 +2007,19 @@
       <c r="B72" t="n">
         <v>0.3588371502263346</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>60%&gt;gen/cap&gt;55%</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>0.2864663327899014</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.3252091815446558</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.3481893248687622</v>
       </c>
     </row>
     <row r="73">
@@ -1231,10 +2027,21 @@
         <v>2594</v>
       </c>
       <c r="B73" t="n">
-        <v>0.9223480455473743</v>
-      </c>
-      <c r="C73" t="n">
+        <v>0.3739692829154674</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>0.2556506736491575</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.3667882038042256</v>
       </c>
     </row>
     <row r="74">
@@ -1244,8 +2051,19 @@
       <c r="B74" t="n">
         <v>0.3821884800577424</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
         <v>0.1867713941993695</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.3711014576249858</v>
       </c>
     </row>
     <row r="75">
@@ -1255,8 +2073,19 @@
       <c r="B75" t="n">
         <v>0.2949961061059678</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
         <v>0.2781918649299595</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.2946721708412444</v>
       </c>
     </row>
     <row r="76">
@@ -1266,8 +2095,19 @@
       <c r="B76" t="n">
         <v>0.3646804787964404</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
         <v>0.3264977314482854</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.3519710018035657</v>
       </c>
     </row>
     <row r="77">
@@ -1275,10 +2115,21 @@
         <v>2527</v>
       </c>
       <c r="B77" t="n">
-        <v>0.4098863214406124</v>
-      </c>
-      <c r="C77" t="n">
+        <v>0.3590409785673437</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>60%&gt;gen/cap&gt;55%</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
         <v>0.1227435804219945</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.3252091815446558</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.3483931532097713</v>
       </c>
     </row>
     <row r="78">
@@ -1288,8 +2139,19 @@
       <c r="B78" t="n">
         <v>0.3663004271672184</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>75%&gt;gen/cap&gt;70%</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
         <v>0.2933406696082255</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.3263565755623398</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.354505207791962</v>
       </c>
     </row>
     <row r="79">
@@ -1299,8 +2161,19 @@
       <c r="B79" t="n">
         <v>0.3456634065261896</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
         <v>0.3012155931624207</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.3329539295333149</v>
       </c>
     </row>
     <row r="80">
@@ -1308,10 +2181,21 @@
         <v>2378</v>
       </c>
       <c r="B80" t="n">
-        <v>0.3453780315850363</v>
-      </c>
-      <c r="C80" t="n">
+        <v>0.3372284753607875</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
         <v>0.3038938519228676</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.3369045400960642</v>
       </c>
     </row>
     <row r="81">
@@ -1321,8 +2205,19 @@
       <c r="B81" t="n">
         <v>0.3525431216392524</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>80%&gt;gen/cap&gt;75%</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
         <v>0.2894672639014496</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.3273807104656135</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.3397237673607223</v>
       </c>
     </row>
     <row r="82">
@@ -1330,10 +2225,21 @@
         <v>2168</v>
       </c>
       <c r="B82" t="n">
-        <v>0.328708041209899</v>
-      </c>
-      <c r="C82" t="n">
+        <v>0.3486868951452934</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>105%&gt;gen/cap&gt;100%</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
         <v>0.3300134796977693</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.2862983427215751</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.3769499086108016</v>
       </c>
     </row>
     <row r="83">
@@ -1343,8 +2249,19 @@
       <c r="B83" t="n">
         <v>0.347242256606984</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>35%&gt;gen/cap&gt;30%</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
         <v>0.3366660226245398</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.318230412532292</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.3435732002617754</v>
       </c>
     </row>
     <row r="84">
@@ -1354,8 +2271,19 @@
       <c r="B84" t="n">
         <v>0.3073561893190898</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
         <v>0.306355634535508</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.337255013572795</v>
       </c>
     </row>
     <row r="85">
@@ -1365,8 +2293,19 @@
       <c r="B85" t="n">
         <v>0.3564376917044341</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>80%&gt;gen/cap&gt;75%</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
         <v>0.2014334174200204</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.3273807104656135</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.3436183374259041</v>
       </c>
     </row>
     <row r="86">
@@ -1376,8 +2315,19 @@
       <c r="B86" t="n">
         <v>0.3895049259438744</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>90%&gt;gen/cap&gt;85%</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
         <v>0.2553359531861112</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.3283053907823258</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.3757608913486319</v>
       </c>
     </row>
     <row r="87">
@@ -1387,8 +2337,19 @@
       <c r="B87" t="n">
         <v>0.3289174670030052</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>90%&gt;gen/cap&gt;85%</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
         <v>0.3240016156437775</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.3283053907823258</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.3151734324077627</v>
       </c>
     </row>
     <row r="88">
@@ -1398,8 +2359,19 @@
       <c r="B88" t="n">
         <v>0.3307078980575056</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
         <v>0.2470961413476412</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.3307078980575057</v>
       </c>
     </row>
     <row r="89">
@@ -1409,8 +2381,19 @@
       <c r="B89" t="n">
         <v>0.2898452909214255</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>90%&gt;gen/cap&gt;85%</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
         <v>0.2693312333619846</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.3283053907823258</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.276101256326183</v>
       </c>
     </row>
     <row r="90">
@@ -1420,8 +2403,19 @@
       <c r="B90" t="n">
         <v>0.3372433879823832</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
         <v>0.3402666492379657</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.3671422122360883</v>
       </c>
     </row>
     <row r="91">
@@ -1431,8 +2425,19 @@
       <c r="B91" t="n">
         <v>0.3958070843343512</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
         <v>0.1957216615609177</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.3862771653209557</v>
       </c>
     </row>
     <row r="92">
@@ -1442,8 +2447,19 @@
       <c r="B92" t="n">
         <v>0.3664351696017946</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>55%&gt;gen/cap&gt;50%</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
         <v>0.3039698100824458</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.3263837145832078</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.3546128112056701</v>
       </c>
     </row>
     <row r="93">
@@ -1451,10 +2467,21 @@
         <v>1912</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3021888497082498</v>
-      </c>
-      <c r="C93" t="n">
+        <v>0.5074215109768669</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>105%&gt;gen/cap&gt;100%</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
         <v>0.1909667217377758</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.2862983427215751</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.5356845244423751</v>
       </c>
     </row>
     <row r="94">
@@ -1464,8 +2491,19 @@
       <c r="B94" t="n">
         <v>0.3464204050467496</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
         <v>0.3432451065086399</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.3763192293004548</v>
       </c>
     </row>
     <row r="95">
@@ -1475,8 +2513,19 @@
       <c r="B95" t="n">
         <v>0.3565804617434754</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
         <v>0.3402237162917815</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.3493993826322337</v>
       </c>
     </row>
     <row r="96">
@@ -1486,8 +2535,19 @@
       <c r="B96" t="n">
         <v>0.3651656580694664</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>90%&gt;gen/cap&gt;85%</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
         <v>0.3225632265749276</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.3283053907823258</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.351421623474224</v>
       </c>
     </row>
     <row r="97">
@@ -1495,10 +2555,21 @@
         <v>1702</v>
       </c>
       <c r="B97" t="n">
-        <v>0.3764542830846391</v>
-      </c>
-      <c r="C97" t="n">
+        <v>0.3676800793748453</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>35%&gt;gen/cap&gt;30%</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
         <v>0.3598111216254937</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.318230412532292</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.3640110230296366</v>
       </c>
     </row>
     <row r="98">
@@ -1508,8 +2579,19 @@
       <c r="B98" t="n">
         <v>0.357139320137509</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
         <v>0.2637338918139669</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.3499582410262673</v>
       </c>
     </row>
     <row r="99">
@@ -1519,8 +2601,19 @@
       <c r="B99" t="n">
         <v>0.4098737004753095</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>75%&gt;gen/cap&gt;70%</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
         <v>0.376655891223158</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.3263565755623398</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.3980784811000532</v>
       </c>
     </row>
     <row r="100">
@@ -1530,8 +2623,19 @@
       <c r="B100" t="n">
         <v>0.4054309772442743</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
         <v>0.272981955302236</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.4353298014979795</v>
       </c>
     </row>
     <row r="101">
@@ -1541,8 +2645,19 @@
       <c r="B101" t="n">
         <v>0.4240297565285431</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
         <v>0.1256978206501678</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.4144998375151476</v>
       </c>
     </row>
     <row r="102">
@@ -1552,8 +2667,19 @@
       <c r="B102" t="n">
         <v>0.3515771891659047</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
         <v>0.3045382009714929</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.3404901667331481</v>
       </c>
     </row>
     <row r="103">
@@ -1563,8 +2689,19 @@
       <c r="B103" t="n">
         <v>0.3216390089905403</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
         <v>0.2214471639605749</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.3144579298792984</v>
       </c>
     </row>
     <row r="104">
@@ -1574,8 +2711,19 @@
       <c r="B104" t="n">
         <v>0.3012247405795566</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
         <v>0.1578897158661545</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.3012247405795566</v>
       </c>
     </row>
     <row r="105">
@@ -1585,8 +2733,19 @@
       <c r="B105" t="n">
         <v>0.3669224493412275</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
         <v>0.2259765394290166</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.3558354269084709</v>
       </c>
     </row>
     <row r="106">
@@ -1596,8 +2755,19 @@
       <c r="B106" t="n">
         <v>0.363290841620831</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>20%&gt;gen/cap&gt;15%</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
         <v>0.04630106772167087</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.2963646942557381</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.3814875035521763</v>
       </c>
     </row>
     <row r="107">
@@ -1607,8 +2777,19 @@
       <c r="B107" t="n">
         <v>0.3668600877894126</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
         <v>0.3329853481097314</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.3665361525246893</v>
       </c>
     </row>
     <row r="108">
@@ -1616,10 +2797,21 @@
         <v>1379</v>
       </c>
       <c r="B108" t="n">
-        <v>0.2793138114026114</v>
-      </c>
-      <c r="C108" t="n">
+        <v>0.2585537627815026</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>25%&gt;gen/cap&gt;20%</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
         <v>0.2146571483550322</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.3086240115132508</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.2644911074553351</v>
       </c>
     </row>
     <row r="109">
@@ -1627,10 +2819,21 @@
         <v>1378</v>
       </c>
       <c r="B109" t="n">
-        <v>0.4844666851906509</v>
-      </c>
-      <c r="C109" t="n">
+        <v>0.3643103252585012</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
         <v>0.207604035415975</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.3547804062451057</v>
       </c>
     </row>
     <row r="110">
@@ -1640,8 +2843,19 @@
       <c r="B110" t="n">
         <v>0.4411933389263253</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
         <v>0.1379510280831988</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.4710921631800304</v>
       </c>
     </row>
     <row r="111">
@@ -1651,8 +2865,19 @@
       <c r="B111" t="n">
         <v>0.2935729852909476</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
         <v>0.1618852517136486</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.2840430662775521</v>
       </c>
     </row>
     <row r="112">
@@ -1660,10 +2885,21 @@
         <v>1356</v>
       </c>
       <c r="B112" t="n">
-        <v>0.3629680822156559</v>
-      </c>
-      <c r="C112" t="n">
+        <v>0.3022058365673728</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>35%&gt;gen/cap&gt;30%</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
         <v>0.2268736178190179</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.318230412532292</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.2985367802221642</v>
       </c>
     </row>
     <row r="113">
@@ -1671,10 +2907,21 @@
         <v>1355</v>
       </c>
       <c r="B113" t="n">
-        <v>0.3309346177964644</v>
-      </c>
-      <c r="C113" t="n">
+        <v>0.3192803264400813</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>55%&gt;gen/cap&gt;50%</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
         <v>0.2974624905930475</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.3263837145832078</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.3074579680439569</v>
       </c>
     </row>
     <row r="114">
@@ -1682,10 +2929,21 @@
         <v>1295</v>
       </c>
       <c r="B114" t="n">
-        <v>0.3681437367799818</v>
-      </c>
-      <c r="C114" t="n">
+        <v>0.315757597302848</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
         <v>0.2434563623102982</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.3456564215565532</v>
       </c>
     </row>
     <row r="115">
@@ -1695,8 +2953,19 @@
       <c r="B115" t="n">
         <v>0.3080239398204193</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
         <v>0.1473971913155392</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.2953144628275446</v>
       </c>
     </row>
     <row r="116">
@@ -1706,8 +2975,19 @@
       <c r="B116" t="n">
         <v>0.3460869864855552</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>85%&gt;gen/cap&gt;80%</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
         <v>0.1587823670799392</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.3287809805955695</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.3318673620770691</v>
       </c>
     </row>
     <row r="117">
@@ -1715,10 +2995,21 @@
         <v>1081</v>
       </c>
       <c r="B117" t="n">
-        <v>0.4210469883460745</v>
-      </c>
-      <c r="C117" t="n">
+        <v>0.3230236292892886</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>50%&gt;gen/cap&gt;45%</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
         <v>0.2348647688883451</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.32492994165991</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.312655043816462</v>
       </c>
     </row>
     <row r="118">
@@ -1728,8 +3019,19 @@
       <c r="B118" t="n">
         <v>0.3589499003075336</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
         <v>0.1559943768226723</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.3462404233146589</v>
       </c>
     </row>
     <row r="119">
@@ -1739,8 +3041,19 @@
       <c r="B119" t="n">
         <v>0.3650582382097938</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
         <v>0.4958270306222222</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3949570624634989</v>
       </c>
     </row>
     <row r="120">
@@ -1750,8 +3063,19 @@
       <c r="B120" t="n">
         <v>0.3516568004615716</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>20%&gt;gen/cap&gt;15%</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
         <v>0.3261285510119878</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.2963646942557381</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3698534623929168</v>
       </c>
     </row>
     <row r="121">
@@ -1761,8 +3085,19 @@
       <c r="B121" t="n">
         <v>0.347803719174677</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
         <v>0.3581886427798633</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3777025434283821</v>
       </c>
     </row>
     <row r="122">
@@ -1772,8 +3107,19 @@
       <c r="B122" t="n">
         <v>0.3750803463378901</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
         <v>0.2596657065481903</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4049791705915953</v>
       </c>
     </row>
     <row r="123">
@@ -1783,8 +3129,19 @@
       <c r="B123" t="n">
         <v>0.3540452759583777</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
         <v>0.3251226295816934</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3429582535256211</v>
       </c>
     </row>
     <row r="124">
@@ -1794,8 +3151,19 @@
       <c r="B124" t="n">
         <v>0.358086273066074</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>40%&gt;gen/cap&gt;35%</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
         <v>0.2689572808377956</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.3217424352983251</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.3509051939548322</v>
       </c>
     </row>
     <row r="125">
@@ -1805,8 +3173,19 @@
       <c r="B125" t="n">
         <v>0.3302489814071</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>85%&gt;gen/cap&gt;80%</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
         <v>0.3195644891973971</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.3287809805955695</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3160293569986138</v>
       </c>
     </row>
     <row r="126">
@@ -1816,8 +3195,19 @@
       <c r="B126" t="n">
         <v>0.3811352610768651</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
         <v>0.3519099099883118</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.4110340853305703</v>
       </c>
     </row>
     <row r="127">
@@ -1825,10 +3215,21 @@
         <v>990</v>
       </c>
       <c r="B127" t="n">
-        <v>0.3580232901520428</v>
-      </c>
-      <c r="C127" t="n">
+        <v>0.3504557586796571</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
         <v>0.2681259085979236</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3393687362469006</v>
       </c>
     </row>
     <row r="128">
@@ -1838,8 +3239,19 @@
       <c r="B128" t="n">
         <v>0.3841926705887183</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>50%&gt;gen/cap&gt;45%</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
         <v>0.2603959862879861</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.32492994165991</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.3738240851158917</v>
       </c>
     </row>
     <row r="129">
@@ -1849,8 +3261,19 @@
       <c r="B129" t="n">
         <v>0.3876880134291685</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
         <v>0.3540329521434992</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.378158094415773</v>
       </c>
     </row>
     <row r="130">
@@ -1858,10 +3281,21 @@
         <v>898</v>
       </c>
       <c r="B130" t="n">
-        <v>0.5115107709985736</v>
-      </c>
-      <c r="C130" t="n">
+        <v>0.329414998932829</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>20%&gt;gen/cap&gt;15%</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
         <v>0.2967417310874794</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.2963646942557381</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3476116608641742</v>
       </c>
     </row>
     <row r="131">
@@ -1871,8 +3305,19 @@
       <c r="B131" t="n">
         <v>0.3118600173462527</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>100%&gt;gen/cap&gt;95%</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
         <v>0.2070189662725886</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3145613561870834</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3118600173462527</v>
       </c>
     </row>
     <row r="132">
@@ -1880,10 +3325,21 @@
         <v>892</v>
       </c>
       <c r="B132" t="n">
-        <v>0.3504047902460523</v>
-      </c>
-      <c r="C132" t="n">
+        <v>0.4279188269462045</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>110%&gt;gen/cap&gt;105%</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
         <v>0.2064178789912281</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.340230792926699</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.4022493902065889</v>
       </c>
     </row>
     <row r="133">
@@ -1893,8 +3349,19 @@
       <c r="B133" t="n">
         <v>0.3572117881186065</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
         <v>0.2563712130177653</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.3445023111257319</v>
       </c>
     </row>
     <row r="134">
@@ -1904,8 +3371,19 @@
       <c r="B134" t="n">
         <v>0.3308272498810406</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
         <v>0.3193416329530831</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.3305033146163173</v>
       </c>
     </row>
     <row r="135">
@@ -1915,8 +3393,19 @@
       <c r="B135" t="n">
         <v>0.4126113671719062</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
         <v>0.2086686432005373</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.4015243447391496</v>
       </c>
     </row>
     <row r="136">
@@ -1924,10 +3413,21 @@
         <v>874</v>
       </c>
       <c r="B136" t="n">
-        <v>0.3473510735948819</v>
-      </c>
-      <c r="C136" t="n">
+        <v>0.3324941606410376</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>45%&gt;gen/cap&gt;40%</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
         <v>0.3094689044471209</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3240912752004788</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3229642416276421</v>
       </c>
     </row>
     <row r="137">
@@ -1937,8 +3437,19 @@
       <c r="B137" t="n">
         <v>0.323541307249837</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>35%&gt;gen/cap&gt;30%</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
         <v>0.2379894155895212</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.318230412532292</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3198722509046285</v>
       </c>
     </row>
     <row r="138">
@@ -1948,8 +3459,19 @@
       <c r="B138" t="n">
         <v>0.3106702622882725</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>30%&gt;gen/cap&gt;25%</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
         <v>0.1920878776622009</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.3148852914518067</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3103463270235493</v>
       </c>
     </row>
     <row r="139">
@@ -1959,8 +3481,19 @@
       <c r="B139" t="n">
         <v>0.4950783493118512</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>90%&gt;gen/cap&gt;85%</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
         <v>0.1991732923717136</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3283053907823258</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.4813343147166088</v>
       </c>
     </row>
     <row r="140">
@@ -1970,8 +3503,19 @@
       <c r="B140" t="n">
         <v>0.3064547503279703</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>85%&gt;gen/cap&gt;80%</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
         <v>0.1749750542175869</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3287809805955695</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.2922351259194841</v>
       </c>
     </row>
     <row r="141">
@@ -1981,8 +3525,19 @@
       <c r="B141" t="n">
         <v>0.4002092710655875</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
         <v>0.3562491197859778</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3874997940727128</v>
       </c>
     </row>
     <row r="142">
@@ -1992,8 +3547,19 @@
       <c r="B142" t="n">
         <v>0.3375460938298391</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>90%&gt;gen/cap&gt;85%</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
         <v>0.294425477771501</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.3283053907823258</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.3238020592345967</v>
       </c>
     </row>
     <row r="143">
@@ -2001,10 +3567,21 @@
         <v>727</v>
       </c>
       <c r="B143" t="n">
-        <v>0.505531634959922</v>
-      </c>
-      <c r="C143" t="n">
+        <v>0.3332092076450067</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>50%&gt;gen/cap&gt;45%</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
         <v>0.193100805461479</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.32492994165991</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3228406221721801</v>
       </c>
     </row>
     <row r="144">
@@ -2014,8 +3591,19 @@
       <c r="B144" t="n">
         <v>0.379943953322869</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>80%&gt;gen/cap&gt;75%</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
         <v>0.08404288861300774</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.3273807104656135</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.3671245990443389</v>
       </c>
     </row>
     <row r="145">
@@ -2025,8 +3613,19 @@
       <c r="B145" t="n">
         <v>0.3645779121458736</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>5%&gt;gen/cap</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
         <v>0.3184158114393266</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.1168752272428449</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.5622640410901121</v>
       </c>
     </row>
     <row r="146">
@@ -2036,8 +3635,19 @@
       <c r="B146" t="n">
         <v>0.3339413851777939</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>80%&gt;gen/cap&gt;75%</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
         <v>0.2798314914285459</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.3273807104656135</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.3211220308992637</v>
       </c>
     </row>
     <row r="147">
@@ -2047,8 +3657,19 @@
       <c r="B147" t="n">
         <v>0.365094891301132</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>60%&gt;gen/cap&gt;55%</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
         <v>0.3611024877373562</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.3252091815446558</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.3544470659435595</v>
       </c>
     </row>
     <row r="148">
@@ -2058,8 +3679,19 @@
       <c r="B148" t="n">
         <v>0.3131411203079891</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
         <v>0.2577908174097741</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.3430399445616943</v>
       </c>
     </row>
     <row r="149">
@@ -2069,8 +3701,19 @@
       <c r="B149" t="n">
         <v>0.3456101174754895</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>20%&gt;gen/cap&gt;15%</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
         <v>0.3088622009420965</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.2963646942557381</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.3638067794068346</v>
       </c>
     </row>
     <row r="150">
@@ -2078,10 +3721,21 @@
         <v>642</v>
       </c>
       <c r="B150" t="n">
-        <v>0.2564508522775998</v>
-      </c>
-      <c r="C150" t="n">
+        <v>0.2575762123781983</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>105%&gt;gen/cap&gt;100%</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
         <v>0.1533984858791717</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.2862983427215751</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.2858392258437065</v>
       </c>
     </row>
     <row r="151">
@@ -2091,8 +3745,19 @@
       <c r="B151" t="n">
         <v>0.3085486849068858</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>85%&gt;gen/cap&gt;80%</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
         <v>0.2522717550407838</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.3287809805955695</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.2943290604983996</v>
       </c>
     </row>
     <row r="152">
@@ -2102,8 +3767,19 @@
       <c r="B152" t="n">
         <v>0.3229707602317733</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>65%&gt;gen/cap&gt;60%</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
         <v>0.1207425987360456</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.32564837861984</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.3118837377990168</v>
       </c>
     </row>
     <row r="153">
@@ -2113,8 +3789,19 @@
       <c r="B153" t="n">
         <v>0.3594231411001607</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>75%&gt;gen/cap&gt;70%</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
         <v>0.366488365190525</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.3263565755623398</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.3476279217249043</v>
       </c>
     </row>
     <row r="154">
@@ -2124,8 +3811,19 @@
       <c r="B154" t="n">
         <v>0.3457479358123071</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>95%&gt;gen/cap&gt;90%</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
         <v>0.3105899521638096</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.327270833179958</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.3330384588194324</v>
       </c>
     </row>
     <row r="155">
@@ -2135,8 +3833,19 @@
       <c r="B155" t="n">
         <v>0.399642350832865</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>15%&gt;gen/cap&gt;10%</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
         <v>0.2255467831244189</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.2846625319333782</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.4295411750865701</v>
       </c>
     </row>
   </sheetData>
